--- a/output/pdf_financials_xlsx/LSPD.xlsx
+++ b/output/pdf_financials_xlsx/LSPD.xlsx
@@ -514,20 +514,30 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D4" s="3" t="n">
-        <v>5.855</v>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>26.866</v>
-      </c>
-      <c r="F4" s="3" t="n">
-        <v>43.959</v>
-      </c>
-      <c r="G4" s="3" t="n">
-        <v>36.515</v>
-      </c>
-      <c r="H4" s="3" t="n">
-        <v>21.317</v>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E4" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F4" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G4" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H4" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -546,20 +556,30 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D5" s="3" t="n">
-        <v>-2.867</v>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>-2.054</v>
-      </c>
-      <c r="F5" s="3" t="n">
-        <v>-1.428</v>
-      </c>
-      <c r="G5" s="3" t="n">
-        <v>-1.481</v>
-      </c>
-      <c r="H5" s="3" t="n">
-        <v>-1.269</v>
+      <c r="D5" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E5" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F5" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G5" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H5" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -957,19 +977,19 @@
         <v>0</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>0</v>
+        <v>5.855</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>0</v>
+        <v>26.866</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>0</v>
+        <v>43.959</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>0</v>
+        <v>36.515</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>0</v>
+        <v>21.317</v>
       </c>
     </row>
     <row r="19">
@@ -1405,19 +1425,19 @@
         <v>-214.254</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>-315.354</v>
+        <v>-321.209</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>-1074.228</v>
+        <v>-1101.094</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>-160.488</v>
+        <v>-204.447</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>-659.509</v>
+        <v>-696.024</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>-144.051</v>
+        <v>-165.368</v>
       </c>
     </row>
     <row r="34">
@@ -1461,19 +1481,19 @@
         <v>-211.106</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>-223.542</v>
+        <v>-229.397</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>-972.682</v>
+        <v>-999.548</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>-65.44</v>
+        <v>-109.399</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>-571.077</v>
+        <v>-607.592</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>-5.227</v>
+        <v>-26.544</v>
       </c>
     </row>
     <row r="36">
@@ -1489,19 +1509,19 @@
         <v>-272.5671715019819</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>-40.76466340367488</v>
+        <v>-41.83236926757748</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>-133.1518153170542</v>
+        <v>-136.8295400722239</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>-7.196982194507682</v>
+        <v>-12.03151979060125</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>-53.03335914994624</v>
+        <v>-56.42434339438312</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>-0.4259824000078237</v>
+        <v>-2.163244083758881</v>
       </c>
     </row>
     <row r="37">
@@ -14704,7 +14724,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -14757,7 +14777,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -15733,7 +15753,7 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
@@ -15782,7 +15802,7 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">

--- a/output/pdf_financials_xlsx/LSPD.xlsx
+++ b/output/pdf_financials_xlsx/LSPD.xlsx
@@ -1447,25 +1447,25 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>3.931</v>
+        <v>5.119</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>3.148</v>
+        <v>4.537</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>91.812</v>
+        <v>104.548</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>101.546</v>
+        <v>115.261</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>95.048</v>
+        <v>109.628</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>88.432</v>
+        <v>100.991</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>138.824</v>
+        <v>150.762</v>
       </c>
     </row>
     <row r="35">
@@ -1475,25 +1475,25 @@
         </is>
       </c>
       <c r="B35" s="3" t="n">
-        <v>-78.002</v>
+        <v>-76.81399999999999</v>
       </c>
       <c r="C35" s="3" t="n">
-        <v>-211.106</v>
+        <v>-209.717</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>-229.397</v>
+        <v>-216.661</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>-999.548</v>
+        <v>-985.833</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>-109.399</v>
+        <v>-94.819</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>-607.592</v>
+        <v>-595.033</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>-26.544</v>
+        <v>-14.606</v>
       </c>
     </row>
     <row r="36">
@@ -1503,25 +1503,25 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>-136.6562133183833</v>
+        <v>-134.5748874367105</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>-272.5671715019819</v>
+        <v>-270.7737795509419</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>-41.83236926757748</v>
+        <v>-39.50985827139241</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>-136.8295400722239</v>
+        <v>-134.9520743156114</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>-12.03151979060125</v>
+        <v>-10.42803567697164</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>-56.42434339438312</v>
+        <v>-55.25804540380711</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>-2.163244083758881</v>
+        <v>-1.190338422520427</v>
       </c>
     </row>
     <row r="37">
@@ -4287,25 +4287,25 @@
         </is>
       </c>
       <c r="B115" s="3" t="n">
-        <v>0</v>
+        <v>5.119</v>
       </c>
       <c r="C115" s="3" t="n">
-        <v>0</v>
+        <v>4.537</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0</v>
+        <v>91.812</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>0</v>
+        <v>101.546</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>0</v>
+        <v>95.048</v>
       </c>
       <c r="G115" s="3" t="n">
-        <v>0</v>
+        <v>88.432</v>
       </c>
       <c r="H115" s="3" t="n">
-        <v>0</v>
+        <v>138.824</v>
       </c>
     </row>
     <row r="116">
@@ -4623,7 +4623,7 @@
         </is>
       </c>
       <c r="B127" s="3" t="n">
-        <v>0</v>
+        <v>0.006</v>
       </c>
       <c r="C127" s="3" t="n">
         <v>0</v>
@@ -9326,7 +9326,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E79" s="5" t="n">
@@ -10063,7 +10063,11 @@
           <t>Additions to intangible assets</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr"/>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E96" s="5" t="n">
         <v>-0.548</v>
       </c>
@@ -11636,7 +11640,11 @@
           <t>Depreciation of property and equipment</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr"/>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E129" s="5" t="n">
         <v>1.188</v>
       </c>
@@ -11685,7 +11693,11 @@
           <t>Loss on disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr"/>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E130" s="5" t="n">
         <v>0.024</v>
       </c>
@@ -11995,7 +12007,11 @@
           <t>Proceeds on disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr"/>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E136" s="5" t="n">
         <v>0.006</v>
       </c>
@@ -13668,7 +13684,11 @@
           <t>Depreciation of property and equipment 13</t>
         </is>
       </c>
-      <c r="D169" t="inlineStr"/>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E169" t="inlineStr">
         <is>
           <t>-</t>
@@ -13717,7 +13737,11 @@
           <t>Depreciation of right-of-use assets 12</t>
         </is>
       </c>
-      <c r="D170" t="inlineStr"/>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E170" t="inlineStr">
         <is>
           <t>-</t>
@@ -13854,7 +13878,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -15077,7 +15101,11 @@
           <t>Depreciation of property and equipment 14</t>
         </is>
       </c>
-      <c r="D198" t="inlineStr"/>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E198" t="inlineStr">
         <is>
           <t>-</t>
@@ -15122,7 +15150,11 @@
           <t>Depreciation of right-of-use assets 13</t>
         </is>
       </c>
-      <c r="D199" t="inlineStr"/>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E199" t="inlineStr">
         <is>
           <t>-</t>
@@ -15222,7 +15254,7 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -16755,7 +16787,11 @@
           <t>Depreciation of property and equipment (note 13)</t>
         </is>
       </c>
-      <c r="D232" t="inlineStr"/>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E232" s="5" t="n">
         <v>1.188</v>
       </c>
@@ -16855,7 +16891,7 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E234" s="5" t="n">

--- a/output/pdf_financials_xlsx/LSPD.xlsx
+++ b/output/pdf_financials_xlsx/LSPD.xlsx
@@ -2933,20 +2933,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D76" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E76" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F76" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D76" s="3" t="n">
+        <v>39.245</v>
+      </c>
+      <c r="E76" s="3" t="n">
+        <v>36.958</v>
+      </c>
+      <c r="F76" s="3" t="n">
+        <v>33.499</v>
       </c>
       <c r="G76" s="1" t="inlineStr">
         <is>
@@ -3171,30 +3165,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D82" s="3" t="n">
+        <v>7.633</v>
+      </c>
+      <c r="E82" s="3" t="n">
+        <v>6.617</v>
+      </c>
+      <c r="F82" s="3" t="n">
+        <v>6.942</v>
+      </c>
+      <c r="G82" s="3" t="n">
+        <v>5.654</v>
+      </c>
+      <c r="H82" s="3" t="n">
+        <v>5.255</v>
       </c>
     </row>
     <row r="83">
@@ -3213,30 +3197,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D83" s="3" t="n">
+        <v>7.633</v>
+      </c>
+      <c r="E83" s="3" t="n">
+        <v>6.617</v>
+      </c>
+      <c r="F83" s="3" t="n">
+        <v>6.942</v>
+      </c>
+      <c r="G83" s="3" t="n">
+        <v>5.654</v>
+      </c>
+      <c r="H83" s="3" t="n">
+        <v>5.255</v>
       </c>
     </row>
     <row r="84">
@@ -3350,19 +3324,19 @@
         <v>24.427</v>
       </c>
       <c r="D87" s="3" t="n">
-        <v>14.351</v>
+        <v>6.718</v>
       </c>
       <c r="E87" s="3" t="n">
-        <v>13.536</v>
+        <v>6.919</v>
       </c>
       <c r="F87" s="3" t="n">
-        <v>8.651</v>
+        <v>1.709</v>
       </c>
       <c r="G87" s="3" t="n">
-        <v>7.194</v>
+        <v>1.54</v>
       </c>
       <c r="H87" s="3" t="n">
-        <v>6.042</v>
+        <v>0.787</v>
       </c>
     </row>
     <row r="88">
@@ -3532,27 +3506,19 @@
         </is>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0.008778600466156306</v>
-      </c>
-      <c r="E92" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F92" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G92" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H92" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.01102407003346876</v>
+      </c>
+      <c r="E92" s="3" t="n">
+        <v>0.002649503553425916</v>
+      </c>
+      <c r="F92" s="3" t="n">
+        <v>0.002877631040610579</v>
+      </c>
+      <c r="G92" s="3" t="n">
+        <v>0.003397903924777354</v>
+      </c>
+      <c r="H92" s="3" t="n">
+        <v>0.003543129766874872</v>
       </c>
     </row>
     <row r="93">
@@ -4489,19 +4455,19 @@
         <v>1.693</v>
       </c>
       <c r="D122" s="3" t="n">
-        <v>0</v>
+        <v>108.916</v>
       </c>
       <c r="E122" s="3" t="n">
-        <v>0</v>
+        <v>129.167</v>
       </c>
       <c r="F122" s="3" t="n">
-        <v>0</v>
+        <v>74.913</v>
       </c>
       <c r="G122" s="3" t="n">
-        <v>0</v>
+        <v>55.605</v>
       </c>
       <c r="H122" s="3" t="n">
-        <v>0</v>
+        <v>57.015</v>
       </c>
     </row>
     <row r="123">
@@ -4892,7 +4858,7 @@
         <v>0</v>
       </c>
       <c r="C136" s="3" t="n">
-        <v>0</v>
+        <v>-0.792</v>
       </c>
       <c r="D136" s="3" t="n">
         <v>0</v>
@@ -6141,7 +6107,11 @@
           <t>Lease liabilities 12</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>-</t>
@@ -7360,7 +7330,11 @@
           <t>Lease liabilities 13</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
           <t>-</t>
@@ -9410,7 +9384,11 @@
           <t>Deferred income tax expense (recovery)</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr"/>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E81" t="inlineStr">
         <is>
           <t>-</t>
@@ -9457,7 +9435,11 @@
           <t>Share-based compensation expense</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr"/>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E82" t="inlineStr">
         <is>
           <t>-</t>
@@ -12062,7 +12044,11 @@
           <t>Repurchase of Common Shares</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr"/>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E137" t="inlineStr">
         <is>
           <t>-</t>
@@ -16334,7 +16320,11 @@
           <t>Total income tax recovery</t>
         </is>
       </c>
-      <c r="D223" t="inlineStr"/>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E223" t="inlineStr">
         <is>
           <t>-</t>
